--- a/data/gravel not enough data/Titici Revo 2025.xlsx
+++ b/data/gravel not enough data/Titici Revo 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel not enough data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E6529E-DF5A-6A46-B706-A61644F10501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAECE3ED-1AA1-0B4D-8D02-A24E89610C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31860" yWindow="-16840" windowWidth="28840" windowHeight="14820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="102">
   <si>
     <t>brand</t>
   </si>
@@ -308,12 +308,6 @@
     <t>integrated</t>
   </si>
   <si>
-    <t>https://www.titici.com/product/revo/</t>
-  </si>
-  <si>
-    <t>https://www.titici.com/wp-content/uploads/2023/09/TITICI-REVO-main.jpg</t>
-  </si>
-  <si>
     <t>XS</t>
   </si>
   <si>
@@ -327,6 +321,24 @@
   </si>
   <si>
     <t>Revo</t>
+  </si>
+  <si>
+    <t>https://www.titici.com/en-eu/collections/revo</t>
+  </si>
+  <si>
+    <t>https://www.titici.com/cdn/shop/files/CGR01RED-02-M_01.png?v=1759414004&amp;width=1000</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>HT</t>
+  </si>
+  <si>
+    <t>Offset</t>
   </si>
 </sst>
 </file>
@@ -685,7 +697,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -709,12 +721,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -722,7 +734,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -733,7 +745,7 @@
         <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
         <v>75</v>
@@ -940,56 +952,132 @@
         <v>400.54</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <f>MEDIAN(H19:H22)</f>
+        <v>391.37900000000002</v>
+      </c>
+      <c r="I17">
+        <f t="shared" ref="I17:K17" si="0">MEDIAN(I19:I22)</f>
+        <v>46.605999999999995</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>1032.2094999999999</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>172.25799999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <v>391.36</v>
+      </c>
+      <c r="I19">
+        <v>45.844999999999999</v>
+      </c>
+      <c r="J19">
+        <v>1031.0229999999999</v>
+      </c>
+      <c r="K19">
+        <v>172.48099999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <v>391.66699999999997</v>
+      </c>
+      <c r="I20">
+        <v>45.53</v>
+      </c>
+      <c r="J20">
+        <v>1035.1220000000001</v>
+      </c>
+      <c r="K20">
+        <v>172.035</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H21">
+        <v>388.202</v>
+      </c>
+      <c r="I21">
+        <v>47.859000000000002</v>
+      </c>
+      <c r="J21">
+        <v>1025.845</v>
+      </c>
+      <c r="K21">
+        <v>169.68199999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
       <c r="E22">
         <v>1110</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <v>391.39800000000002</v>
+      </c>
+      <c r="I22">
+        <v>47.366999999999997</v>
+      </c>
+      <c r="J22">
+        <v>1033.396</v>
+      </c>
+      <c r="K22">
+        <v>172.87799999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -997,18 +1085,18 @@
         <v>700</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>24</v>
       </c>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -1028,7 +1116,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -1048,7 +1136,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>29</v>
       </c>
@@ -1085,7 +1173,7 @@
         <v>31</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -1163,7 +1251,7 @@
         <v>42</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
